--- a/Unity/Assets/Config/Excel/ExpConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ExpConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ExpProto" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,14 +245,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,48 +490,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1176,346 +1128,346 @@
     <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -1640,7 +1592,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1703,64 +1655,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2172,7 +2124,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8D985DB0-0755-45DF-ABF9-C611883F447F}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{9D3CEE6F-C691-4E0D-B4EB-C143029307C2}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2472,7 +2424,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2521,703 +2473,713 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="2:5">
       <c r="B4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="6">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="2:5">
       <c r="B5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="6">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="2:5">
       <c r="B6" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="6">
-        <v>1125</v>
+        <v>500</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="2:5">
       <c r="B7" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="6">
-        <v>1350</v>
+        <v>1125</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="2:5">
       <c r="B8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="6">
-        <v>2600</v>
+        <v>1350</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="2:5">
       <c r="B9" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6">
-        <v>4250</v>
+        <v>2600</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="2:5">
       <c r="B10" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6">
-        <v>6600</v>
+        <v>4250</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="2:5">
       <c r="B11" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="6">
-        <v>8400</v>
+        <v>6600</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="2:5">
       <c r="B12" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>10000</v>
+        <v>8400</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="2:5">
       <c r="B13" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>12825</v>
+        <v>10000</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="2:5">
       <c r="B14" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>16060</v>
+        <v>12825</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="2:5">
       <c r="B15" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>19500</v>
+        <v>16060</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="2:5">
       <c r="B16" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="6">
-        <v>22400</v>
+        <v>19500</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="2:5">
       <c r="B17" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="6">
-        <v>27280</v>
+        <v>22400</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="2:5">
       <c r="B18" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="6">
-        <v>47420</v>
+        <v>27280</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="2:5">
       <c r="B19" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="6">
-        <v>54380</v>
+        <v>47420</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="2:5">
       <c r="B20" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6">
-        <v>61740</v>
+        <v>54380</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="2:5">
       <c r="B21" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="6">
-        <v>69500</v>
+        <v>61740</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="2:5">
       <c r="B22" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="6">
-        <v>110300</v>
+        <v>69500</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="2:5">
       <c r="B23" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="6">
-        <v>122220</v>
+        <v>110300</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="2:5">
       <c r="B24" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="6">
-        <v>135050</v>
+        <v>122220</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="2:5">
       <c r="B25" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="6">
-        <v>148200</v>
+        <v>135050</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="2:5">
       <c r="B26" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="6">
-        <v>161950</v>
+        <v>148200</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="2:5">
       <c r="B27" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="6">
-        <v>176300</v>
+        <v>161950</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="2:5">
       <c r="B28" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>191250</v>
+        <v>176300</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="2:5">
       <c r="B29" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="6">
-        <v>207260</v>
+        <v>191250</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="2:5">
       <c r="B30" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>223440</v>
+        <v>207260</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="2:5">
       <c r="B31" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="6">
-        <v>240220</v>
+        <v>223440</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="2:5">
       <c r="B32" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="6">
-        <v>299800</v>
+        <v>240220</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="2:5">
       <c r="B33" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="6">
-        <v>432680</v>
+        <v>299800</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="2:5">
       <c r="B34" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="6">
-        <v>456520</v>
+        <v>432680</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="2:5">
       <c r="B35" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="6">
-        <v>480380</v>
+        <v>456520</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="2:5">
       <c r="B36" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="6">
-        <v>504840</v>
+        <v>480380</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="2:5">
       <c r="B37" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="6">
-        <v>529900</v>
+        <v>504840</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="2:5">
       <c r="B38" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="6">
-        <v>555560</v>
+        <v>529900</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="2:5">
       <c r="B39" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="6">
-        <v>582580</v>
+        <v>555560</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="2:5">
       <c r="B40" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="6">
-        <v>609470</v>
+        <v>582580</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="2:5">
       <c r="B41" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="6">
-        <v>636960</v>
+        <v>609470</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="2:5">
       <c r="B42" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="6">
-        <v>738000</v>
+        <v>636960</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="2:5">
       <c r="B43" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="6">
-        <v>928840</v>
+        <v>738000</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="2:5">
       <c r="B44" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="6">
-        <v>962780</v>
+        <v>928840</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="2:5">
       <c r="B45" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="6">
-        <v>997320</v>
+        <v>962780</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="2:5">
       <c r="B46" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" s="6">
-        <v>1032460</v>
+        <v>997320</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="2:5">
       <c r="B47" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="6">
-        <v>1068200</v>
+        <v>1032460</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="2:5">
       <c r="B48" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="6">
-        <v>1104540</v>
+        <v>1068200</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="2:5">
       <c r="B49" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="6">
-        <v>1141480</v>
+        <v>1104540</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="2:5">
       <c r="B50" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" s="6">
-        <v>1179020</v>
+        <v>1141480</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="2:5">
       <c r="B51" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" s="6">
-        <v>1217160</v>
+        <v>1179020</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="2:5">
       <c r="B52" s="5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" s="6">
-        <v>1463300</v>
+        <v>1217160</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="2:5">
       <c r="B53" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" s="6">
-        <v>1826050</v>
+        <v>1463300</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="2:5">
       <c r="B54" s="5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C54" s="6">
-        <v>1971300</v>
+        <v>1826050</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="2:5">
       <c r="B55" s="5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55" s="6">
-        <v>2243500</v>
+        <v>1971300</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="2:5">
       <c r="B56" s="5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" s="6">
-        <v>2521700</v>
+        <v>2243500</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="2:5">
       <c r="B57" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="6">
-        <v>2805900</v>
+        <v>2521700</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="2:5">
       <c r="B58" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C58" s="6">
-        <v>3096100</v>
+        <v>2805900</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="2:5">
       <c r="B59" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C59" s="6">
-        <v>3392300</v>
+        <v>3096100</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="2:5">
       <c r="B60" s="5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="6">
-        <v>3694500</v>
+        <v>3392300</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="2:5">
       <c r="B61" s="5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="6">
-        <v>4268600</v>
+        <v>3694500</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="2:5">
       <c r="B62" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" s="6">
-        <v>4854700</v>
+        <v>4268600</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="2:5">
       <c r="B63" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" s="6">
-        <v>5452800</v>
+        <v>4854700</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="2:5">
       <c r="B64" s="5">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C64" s="6">
-        <v>6887600</v>
+        <v>5452800</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="2:5">
       <c r="B65" s="5">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" s="6">
-        <v>9186100</v>
+        <v>6887600</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="2:5">
       <c r="B66" s="5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="6">
-        <v>12094400</v>
+        <v>9186100</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="2:5">
       <c r="B67" s="5">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C67" s="6">
-        <v>15630500</v>
+        <v>12094400</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="2:5">
       <c r="B68" s="5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C68" s="6">
-        <v>20099300</v>
+        <v>15630500</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="2:5">
       <c r="B69" s="5">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C69" s="6">
-        <v>26091000</v>
+        <v>20099300</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="2:5">
       <c r="B70" s="5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="6">
-        <v>35148000</v>
+        <v>26091000</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="2:5">
       <c r="B71" s="5">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" s="6">
-        <v>47344000</v>
+        <v>35148000</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="2:5">
       <c r="B72" s="5">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C72" s="6">
-        <v>59780000</v>
+        <v>47344000</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="2:5">
       <c r="B73" s="5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C73" s="6">
-        <v>75475000</v>
+        <v>59780000</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
+    </row>
+    <row r="74" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B74" s="5">
+        <v>70</v>
+      </c>
+      <c r="C74" s="6">
+        <v>75475000</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/ExpConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ExpConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="ExpProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>##var</t>
   </si>
@@ -35,7 +35,10 @@
     <t>Id</t>
   </si>
   <si>
-    <t>UpExp</t>
+    <t>PlayerUpExp</t>
+  </si>
+  <si>
+    <t>HeroUpExp</t>
   </si>
   <si>
     <t>##type</t>
@@ -47,7 +50,10 @@
     <t>##</t>
   </si>
   <si>
-    <t>角色升级经验</t>
+    <t>玩家升级经验</t>
+  </si>
+  <si>
+    <t>英雄升级经验</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2130,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{9D3CEE6F-C691-4E0D-B4EB-C143029307C2}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{042176B7-D764-4A60-A9A6-D41C9AA41424}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2428,12 +2434,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="3" max="4" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="13.125" style="1" customWidth="1"/>
     <col min="6" max="8" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" spans="1:3">
+    <row r="1" ht="20.1" customHeight="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2443,29 +2449,37 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="20.1" customHeight="1" spans="1:3">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3"/>
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -2478,7 +2492,9 @@
       <c r="C4" s="6">
         <v>0</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="2:5">
@@ -2488,7 +2504,9 @@
       <c r="C5" s="6">
         <v>225</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6">
+        <v>225</v>
+      </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="2:5">
@@ -2498,7 +2516,9 @@
       <c r="C6" s="6">
         <v>500</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6">
+        <v>500</v>
+      </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="2:5">
@@ -2508,7 +2528,9 @@
       <c r="C7" s="6">
         <v>1125</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6">
+        <v>1125</v>
+      </c>
       <c r="E7" s="6"/>
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="2:5">
@@ -2518,7 +2540,9 @@
       <c r="C8" s="6">
         <v>1350</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6">
+        <v>1350</v>
+      </c>
       <c r="E8" s="6"/>
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="2:5">
@@ -2528,7 +2552,9 @@
       <c r="C9" s="6">
         <v>2600</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6">
+        <v>2600</v>
+      </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="2:5">
@@ -2538,7 +2564,9 @@
       <c r="C10" s="6">
         <v>4250</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6">
+        <v>4250</v>
+      </c>
       <c r="E10" s="6"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="2:5">
@@ -2548,7 +2576,9 @@
       <c r="C11" s="6">
         <v>6600</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6">
+        <v>6600</v>
+      </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="2:5">
@@ -2558,7 +2588,9 @@
       <c r="C12" s="6">
         <v>8400</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6">
+        <v>8400</v>
+      </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="2:5">
@@ -2568,7 +2600,9 @@
       <c r="C13" s="6">
         <v>10000</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6">
+        <v>10000</v>
+      </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="2:5">
@@ -2578,7 +2612,9 @@
       <c r="C14" s="6">
         <v>12825</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6">
+        <v>12825</v>
+      </c>
       <c r="E14" s="6"/>
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="2:5">
@@ -2588,7 +2624,9 @@
       <c r="C15" s="6">
         <v>16060</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="6">
+        <v>16060</v>
+      </c>
       <c r="E15" s="6"/>
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="2:5">
@@ -2598,7 +2636,9 @@
       <c r="C16" s="6">
         <v>19500</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6">
+        <v>19500</v>
+      </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="2:5">
@@ -2608,7 +2648,9 @@
       <c r="C17" s="6">
         <v>22400</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="6">
+        <v>22400</v>
+      </c>
       <c r="E17" s="6"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="2:5">
@@ -2618,7 +2660,9 @@
       <c r="C18" s="6">
         <v>27280</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="6">
+        <v>27280</v>
+      </c>
       <c r="E18" s="6"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="2:5">
@@ -2628,7 +2672,9 @@
       <c r="C19" s="6">
         <v>47420</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="6">
+        <v>47420</v>
+      </c>
       <c r="E19" s="6"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="2:5">
@@ -2638,7 +2684,9 @@
       <c r="C20" s="6">
         <v>54380</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="6">
+        <v>54380</v>
+      </c>
       <c r="E20" s="6"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="2:5">
@@ -2648,7 +2696,9 @@
       <c r="C21" s="6">
         <v>61740</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="6">
+        <v>61740</v>
+      </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="2:5">
@@ -2658,7 +2708,9 @@
       <c r="C22" s="6">
         <v>69500</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="6">
+        <v>69500</v>
+      </c>
       <c r="E22" s="6"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="2:5">
@@ -2668,7 +2720,9 @@
       <c r="C23" s="6">
         <v>110300</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6">
+        <v>110300</v>
+      </c>
       <c r="E23" s="6"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="2:5">
@@ -2678,7 +2732,9 @@
       <c r="C24" s="6">
         <v>122220</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6">
+        <v>122220</v>
+      </c>
       <c r="E24" s="6"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="2:5">
@@ -2688,7 +2744,9 @@
       <c r="C25" s="6">
         <v>135050</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6">
+        <v>135050</v>
+      </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="2:5">
@@ -2698,7 +2756,9 @@
       <c r="C26" s="6">
         <v>148200</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6">
+        <v>148200</v>
+      </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="2:5">
@@ -2708,7 +2768,9 @@
       <c r="C27" s="6">
         <v>161950</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="6">
+        <v>161950</v>
+      </c>
       <c r="E27" s="6"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="2:5">
@@ -2718,7 +2780,9 @@
       <c r="C28" s="6">
         <v>176300</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="6">
+        <v>176300</v>
+      </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="2:5">
@@ -2728,7 +2792,9 @@
       <c r="C29" s="6">
         <v>191250</v>
       </c>
-      <c r="D29" s="6"/>
+      <c r="D29" s="6">
+        <v>191250</v>
+      </c>
       <c r="E29" s="6"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="2:5">
@@ -2738,7 +2804,9 @@
       <c r="C30" s="6">
         <v>207260</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="6">
+        <v>207260</v>
+      </c>
       <c r="E30" s="6"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="2:5">
@@ -2748,7 +2816,9 @@
       <c r="C31" s="6">
         <v>223440</v>
       </c>
-      <c r="D31" s="6"/>
+      <c r="D31" s="6">
+        <v>223440</v>
+      </c>
       <c r="E31" s="6"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="2:5">
@@ -2758,7 +2828,9 @@
       <c r="C32" s="6">
         <v>240220</v>
       </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="6">
+        <v>240220</v>
+      </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="2:5">
@@ -2768,7 +2840,9 @@
       <c r="C33" s="6">
         <v>299800</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="6">
+        <v>299800</v>
+      </c>
       <c r="E33" s="6"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" spans="2:5">
@@ -2778,7 +2852,9 @@
       <c r="C34" s="6">
         <v>432680</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="6">
+        <v>432680</v>
+      </c>
       <c r="E34" s="6"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="2:5">
@@ -2788,7 +2864,9 @@
       <c r="C35" s="6">
         <v>456520</v>
       </c>
-      <c r="D35" s="6"/>
+      <c r="D35" s="6">
+        <v>456520</v>
+      </c>
       <c r="E35" s="6"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" spans="2:5">
@@ -2798,7 +2876,9 @@
       <c r="C36" s="6">
         <v>480380</v>
       </c>
-      <c r="D36" s="6"/>
+      <c r="D36" s="6">
+        <v>480380</v>
+      </c>
       <c r="E36" s="6"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" spans="2:5">
@@ -2808,7 +2888,9 @@
       <c r="C37" s="6">
         <v>504840</v>
       </c>
-      <c r="D37" s="6"/>
+      <c r="D37" s="6">
+        <v>504840</v>
+      </c>
       <c r="E37" s="6"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="2:5">
@@ -2818,7 +2900,9 @@
       <c r="C38" s="6">
         <v>529900</v>
       </c>
-      <c r="D38" s="6"/>
+      <c r="D38" s="6">
+        <v>529900</v>
+      </c>
       <c r="E38" s="6"/>
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="2:5">
@@ -2828,7 +2912,9 @@
       <c r="C39" s="6">
         <v>555560</v>
       </c>
-      <c r="D39" s="6"/>
+      <c r="D39" s="6">
+        <v>555560</v>
+      </c>
       <c r="E39" s="6"/>
     </row>
     <row r="40" ht="20.1" customHeight="1" spans="2:5">
@@ -2838,7 +2924,9 @@
       <c r="C40" s="6">
         <v>582580</v>
       </c>
-      <c r="D40" s="6"/>
+      <c r="D40" s="6">
+        <v>582580</v>
+      </c>
       <c r="E40" s="6"/>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="2:5">
@@ -2848,7 +2936,9 @@
       <c r="C41" s="6">
         <v>609470</v>
       </c>
-      <c r="D41" s="6"/>
+      <c r="D41" s="6">
+        <v>609470</v>
+      </c>
       <c r="E41" s="6"/>
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="2:5">
@@ -2858,7 +2948,9 @@
       <c r="C42" s="6">
         <v>636960</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6">
+        <v>636960</v>
+      </c>
       <c r="E42" s="6"/>
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="2:5">
@@ -2868,7 +2960,9 @@
       <c r="C43" s="6">
         <v>738000</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="6">
+        <v>738000</v>
+      </c>
       <c r="E43" s="6"/>
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="2:5">
@@ -2878,7 +2972,9 @@
       <c r="C44" s="6">
         <v>928840</v>
       </c>
-      <c r="D44" s="6"/>
+      <c r="D44" s="6">
+        <v>928840</v>
+      </c>
       <c r="E44" s="6"/>
     </row>
     <row r="45" ht="20.1" customHeight="1" spans="2:5">
@@ -2888,7 +2984,9 @@
       <c r="C45" s="6">
         <v>962780</v>
       </c>
-      <c r="D45" s="6"/>
+      <c r="D45" s="6">
+        <v>962780</v>
+      </c>
       <c r="E45" s="6"/>
     </row>
     <row r="46" ht="20.1" customHeight="1" spans="2:5">
@@ -2898,7 +2996,9 @@
       <c r="C46" s="6">
         <v>997320</v>
       </c>
-      <c r="D46" s="6"/>
+      <c r="D46" s="6">
+        <v>997320</v>
+      </c>
       <c r="E46" s="6"/>
     </row>
     <row r="47" ht="20.1" customHeight="1" spans="2:5">
@@ -2908,7 +3008,9 @@
       <c r="C47" s="6">
         <v>1032460</v>
       </c>
-      <c r="D47" s="6"/>
+      <c r="D47" s="6">
+        <v>1032460</v>
+      </c>
       <c r="E47" s="6"/>
     </row>
     <row r="48" ht="20.1" customHeight="1" spans="2:5">
@@ -2918,7 +3020,9 @@
       <c r="C48" s="6">
         <v>1068200</v>
       </c>
-      <c r="D48" s="6"/>
+      <c r="D48" s="6">
+        <v>1068200</v>
+      </c>
       <c r="E48" s="6"/>
     </row>
     <row r="49" ht="20.1" customHeight="1" spans="2:5">
@@ -2928,7 +3032,9 @@
       <c r="C49" s="6">
         <v>1104540</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="6">
+        <v>1104540</v>
+      </c>
       <c r="E49" s="6"/>
     </row>
     <row r="50" ht="20.1" customHeight="1" spans="2:5">
@@ -2938,7 +3044,9 @@
       <c r="C50" s="6">
         <v>1141480</v>
       </c>
-      <c r="D50" s="6"/>
+      <c r="D50" s="6">
+        <v>1141480</v>
+      </c>
       <c r="E50" s="6"/>
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="2:5">
@@ -2948,7 +3056,9 @@
       <c r="C51" s="6">
         <v>1179020</v>
       </c>
-      <c r="D51" s="6"/>
+      <c r="D51" s="6">
+        <v>1179020</v>
+      </c>
       <c r="E51" s="6"/>
     </row>
     <row r="52" ht="20.1" customHeight="1" spans="2:5">
@@ -2958,7 +3068,9 @@
       <c r="C52" s="6">
         <v>1217160</v>
       </c>
-      <c r="D52" s="6"/>
+      <c r="D52" s="6">
+        <v>1217160</v>
+      </c>
       <c r="E52" s="6"/>
     </row>
     <row r="53" ht="20.1" customHeight="1" spans="2:5">
@@ -2968,7 +3080,9 @@
       <c r="C53" s="6">
         <v>1463300</v>
       </c>
-      <c r="D53" s="6"/>
+      <c r="D53" s="6">
+        <v>1463300</v>
+      </c>
       <c r="E53" s="6"/>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="2:5">
@@ -2978,7 +3092,9 @@
       <c r="C54" s="6">
         <v>1826050</v>
       </c>
-      <c r="D54" s="6"/>
+      <c r="D54" s="6">
+        <v>1826050</v>
+      </c>
       <c r="E54" s="6"/>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="2:5">
@@ -2988,7 +3104,9 @@
       <c r="C55" s="6">
         <v>1971300</v>
       </c>
-      <c r="D55" s="6"/>
+      <c r="D55" s="6">
+        <v>1971300</v>
+      </c>
       <c r="E55" s="6"/>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="2:5">
@@ -2998,7 +3116,9 @@
       <c r="C56" s="6">
         <v>2243500</v>
       </c>
-      <c r="D56" s="6"/>
+      <c r="D56" s="6">
+        <v>2243500</v>
+      </c>
       <c r="E56" s="6"/>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="2:5">
@@ -3008,7 +3128,9 @@
       <c r="C57" s="6">
         <v>2521700</v>
       </c>
-      <c r="D57" s="6"/>
+      <c r="D57" s="6">
+        <v>2521700</v>
+      </c>
       <c r="E57" s="6"/>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="2:5">
@@ -3018,7 +3140,9 @@
       <c r="C58" s="6">
         <v>2805900</v>
       </c>
-      <c r="D58" s="6"/>
+      <c r="D58" s="6">
+        <v>2805900</v>
+      </c>
       <c r="E58" s="6"/>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="2:5">
@@ -3028,7 +3152,9 @@
       <c r="C59" s="6">
         <v>3096100</v>
       </c>
-      <c r="D59" s="6"/>
+      <c r="D59" s="6">
+        <v>3096100</v>
+      </c>
       <c r="E59" s="6"/>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="2:5">
@@ -3038,7 +3164,9 @@
       <c r="C60" s="6">
         <v>3392300</v>
       </c>
-      <c r="D60" s="6"/>
+      <c r="D60" s="6">
+        <v>3392300</v>
+      </c>
       <c r="E60" s="6"/>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="2:5">
@@ -3048,7 +3176,9 @@
       <c r="C61" s="6">
         <v>3694500</v>
       </c>
-      <c r="D61" s="6"/>
+      <c r="D61" s="6">
+        <v>3694500</v>
+      </c>
       <c r="E61" s="6"/>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="2:5">
@@ -3058,7 +3188,9 @@
       <c r="C62" s="6">
         <v>4268600</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="D62" s="6">
+        <v>4268600</v>
+      </c>
       <c r="E62" s="6"/>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="2:5">
@@ -3068,7 +3200,9 @@
       <c r="C63" s="6">
         <v>4854700</v>
       </c>
-      <c r="D63" s="6"/>
+      <c r="D63" s="6">
+        <v>4854700</v>
+      </c>
       <c r="E63" s="6"/>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="2:5">
@@ -3078,7 +3212,9 @@
       <c r="C64" s="6">
         <v>5452800</v>
       </c>
-      <c r="D64" s="6"/>
+      <c r="D64" s="6">
+        <v>5452800</v>
+      </c>
       <c r="E64" s="6"/>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="2:5">
@@ -3088,7 +3224,9 @@
       <c r="C65" s="6">
         <v>6887600</v>
       </c>
-      <c r="D65" s="6"/>
+      <c r="D65" s="6">
+        <v>6887600</v>
+      </c>
       <c r="E65" s="6"/>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="2:5">
@@ -3098,7 +3236,9 @@
       <c r="C66" s="6">
         <v>9186100</v>
       </c>
-      <c r="D66" s="6"/>
+      <c r="D66" s="6">
+        <v>9186100</v>
+      </c>
       <c r="E66" s="6"/>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="2:5">
@@ -3108,7 +3248,9 @@
       <c r="C67" s="6">
         <v>12094400</v>
       </c>
-      <c r="D67" s="6"/>
+      <c r="D67" s="6">
+        <v>12094400</v>
+      </c>
       <c r="E67" s="6"/>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="2:5">
@@ -3118,7 +3260,9 @@
       <c r="C68" s="6">
         <v>15630500</v>
       </c>
-      <c r="D68" s="6"/>
+      <c r="D68" s="6">
+        <v>15630500</v>
+      </c>
       <c r="E68" s="6"/>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="2:5">
@@ -3128,7 +3272,9 @@
       <c r="C69" s="6">
         <v>20099300</v>
       </c>
-      <c r="D69" s="6"/>
+      <c r="D69" s="6">
+        <v>20099300</v>
+      </c>
       <c r="E69" s="6"/>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="2:5">
@@ -3138,7 +3284,9 @@
       <c r="C70" s="6">
         <v>26091000</v>
       </c>
-      <c r="D70" s="6"/>
+      <c r="D70" s="6">
+        <v>26091000</v>
+      </c>
       <c r="E70" s="6"/>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="2:5">
@@ -3148,7 +3296,9 @@
       <c r="C71" s="6">
         <v>35148000</v>
       </c>
-      <c r="D71" s="6"/>
+      <c r="D71" s="6">
+        <v>35148000</v>
+      </c>
       <c r="E71" s="6"/>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="2:5">
@@ -3158,7 +3308,9 @@
       <c r="C72" s="6">
         <v>47344000</v>
       </c>
-      <c r="D72" s="6"/>
+      <c r="D72" s="6">
+        <v>47344000</v>
+      </c>
       <c r="E72" s="6"/>
     </row>
     <row r="73" ht="20.1" customHeight="1" spans="2:5">
@@ -3168,7 +3320,9 @@
       <c r="C73" s="6">
         <v>59780000</v>
       </c>
-      <c r="D73" s="6"/>
+      <c r="D73" s="6">
+        <v>59780000</v>
+      </c>
       <c r="E73" s="6"/>
     </row>
     <row r="74" ht="20.1" customHeight="1" spans="2:5">
@@ -3178,7 +3332,9 @@
       <c r="C74" s="6">
         <v>75475000</v>
       </c>
-      <c r="D74" s="6"/>
+      <c r="D74" s="6">
+        <v>75475000</v>
+      </c>
       <c r="E74" s="6"/>
     </row>
   </sheetData>
